--- a/templates/2026建行表格模板.xlsx
+++ b/templates/2026建行表格模板.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celem\Documents\wage_excel_helper\dist\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celem\Documents\wage_excel_helper\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3A565C2-C8F8-4830-A410-5645EC2F239D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7961E9-4643-4A7C-9930-83753D673E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{204DA2BD-E2CB-4C1A-B365-E4CFA3F01B10}"/>
   </bookViews>
@@ -19,24 +19,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet0!$B$1:$B$24</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
-    <t>序号（必填）</t>
-  </si>
-  <si>
     <t>账号（必填）</t>
   </si>
   <si>
@@ -180,6 +168,10 @@
   </si>
   <si>
     <t>6225680822000587148</t>
+  </si>
+  <si>
+    <t>序号（必填）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -187,9 +179,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="180" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -218,6 +210,12 @@
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -262,7 +260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -270,33 +268,29 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -810,530 +804,530 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="12" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="7"/>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="J2" s="4"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="7"/>
-      <c r="J2" s="4"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="7"/>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="J3" s="4"/>
+    </row>
+    <row r="4" spans="1:10" s="1" customFormat="1">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="7"/>
-      <c r="J3" s="4"/>
-    </row>
-    <row r="4" spans="1:10" s="1" customFormat="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="7"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="J4" s="4"/>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="7"/>
-      <c r="J4" s="4"/>
-    </row>
-    <row r="5" spans="1:10" s="1" customFormat="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="7"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="J5" s="5"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="7"/>
-      <c r="J5" s="5"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="7"/>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="7"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="J6" s="4"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="7"/>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="7"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="J7" s="4"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="7"/>
-      <c r="J7" s="4"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="7"/>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="3"/>
+      <c r="J8" s="4"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="7"/>
-      <c r="J8" s="4"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="7"/>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="7"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="J9" s="4"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="7"/>
-      <c r="J9" s="4"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="7"/>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="7"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="7"/>
-      <c r="J10" s="4"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="7"/>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="7"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="7"/>
-      <c r="J11" s="4"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="7"/>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="7"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="7"/>
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="7"/>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="7"/>
-      <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="7"/>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="7"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="6"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="8"/>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="7"/>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="7"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="6"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="8"/>
-      <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="7"/>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="7"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="8"/>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="10"/>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7" t="s">
+      <c r="C17" s="7"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="3"/>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="7"/>
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="7"/>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="7"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="7"/>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="7"/>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="7"/>
-      <c r="B19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="9"/>
-      <c r="J19" s="4"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="7"/>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="7"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="7"/>
-      <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="7"/>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="7"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="3"/>
+      <c r="B22" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="7"/>
-      <c r="J21" s="4"/>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="7"/>
-      <c r="B22" s="11" t="s">
+      <c r="C22" s="7"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="3"/>
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="7"/>
-      <c r="J22" s="4"/>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="7"/>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="7"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="7"/>
-      <c r="J23" s="4"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="7"/>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="7"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="7"/>
-      <c r="J24" s="4"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7" t="s">
+      <c r="C25" s="11"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="7"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7" t="s">
+      <c r="C26" s="11"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="7"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7" t="s">
+      <c r="C27" s="11"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7" t="s">
+      <c r="C28" s="11"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+    </row>
+    <row r="29" spans="1:10" ht="12" customHeight="1">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-    </row>
-    <row r="29" spans="1:10" ht="12" customHeight="1">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7" t="s">
+      <c r="C29" s="11"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="3"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="13"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="7"/>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7" t="s">
+      <c r="C30" s="11"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="3"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="7"/>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7" t="s">
+      <c r="C31" s="11"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="11"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="13"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="7"/>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7" t="s">
+      <c r="C33" s="11"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7" t="s">
+      <c r="C34" s="11"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="13"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7" t="s">
+      <c r="C35" s="11"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="13"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7" t="s">
+      <c r="C36" s="11"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7" t="s">
+      <c r="C37" s="11"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="7"/>
-      <c r="B38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" s="13"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="17"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="14"/>
       <c r="G38" s="3"/>
-      <c r="H38" s="7"/>
+      <c r="H38" s="3"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="7"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
